--- a/美股港股报告_20260922.xlsx
+++ b/美股港股报告_20260922.xlsx
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="E10" t="n">
         <v>19.91</v>
@@ -842,7 +842,7 @@
         <v>1.23</v>
       </c>
       <c r="G10" t="n">
-        <v>0.379</v>
+        <v>0.38</v>
       </c>
       <c r="H10" t="n">
         <v>1</v>
@@ -968,7 +968,7 @@
         <v>5.85</v>
       </c>
       <c r="G13" t="n">
-        <v>0.438</v>
+        <v>0.44</v>
       </c>
       <c r="H13" t="n">
         <v>1</v>
@@ -1085,7 +1085,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="E16" t="n">
         <v>12.63</v>
@@ -1094,7 +1094,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.764</v>
+        <v>0.767</v>
       </c>
       <c r="H16" t="n">
         <v>0.75</v>

--- a/美股港股报告_20260922.xlsx
+++ b/美股港股报告_20260922.xlsx
@@ -539,16 +539,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.85</v>
+        <v>18.05</v>
       </c>
       <c r="E3" t="n">
         <v>104.3</v>
       </c>
       <c r="F3" t="n">
-        <v>3.11</v>
+        <v>3.14</v>
       </c>
       <c r="G3" t="n">
-        <v>0.129</v>
+        <v>0.13</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
@@ -581,7 +581,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>6.97</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
         <v>48.68</v>
@@ -590,7 +590,7 @@
         <v>25</v>
       </c>
       <c r="G4" t="n">
-        <v>0.159</v>
+        <v>0.16</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>46.06</v>
+        <v>46.6</v>
       </c>
       <c r="E5" t="n">
         <v>148.75</v>
@@ -632,7 +632,7 @@
         <v>32</v>
       </c>
       <c r="G5" t="n">
-        <v>0.198</v>
+        <v>0.201</v>
       </c>
       <c r="H5" t="n">
         <v>0.75</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="E6" t="n">
         <v>16.81</v>
@@ -674,7 +674,7 @@
         <v>6.22</v>
       </c>
       <c r="G6" t="n">
-        <v>0.253</v>
+        <v>0.25</v>
       </c>
       <c r="H6" t="n">
         <v>1</v>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5.05</v>
+        <v>4.98</v>
       </c>
       <c r="E7" t="n">
         <v>30.56</v>
@@ -716,7 +716,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.308</v>
+        <v>0.304</v>
       </c>
       <c r="H7" t="n">
         <v>1</v>
@@ -735,30 +735,30 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0939.HK</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0939.HK</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>港股</t>
+          <t>美股</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.61</v>
+        <v>8.33</v>
       </c>
       <c r="E8" t="n">
-        <v>9.4</v>
+        <v>34.04</v>
       </c>
       <c r="F8" t="n">
-        <v>4.5</v>
+        <v>78</v>
       </c>
       <c r="G8" t="n">
-        <v>0.36</v>
+        <v>0.357</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
@@ -777,30 +777,30 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>0939.HK</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>0939.HK</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>美股</t>
+          <t>港股</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>8.42</v>
+        <v>0.61</v>
       </c>
       <c r="E9" t="n">
-        <v>34.04</v>
+        <v>9.4</v>
       </c>
       <c r="F9" t="n">
-        <v>79</v>
+        <v>4.5</v>
       </c>
       <c r="G9" t="n">
-        <v>0.361</v>
+        <v>0.359</v>
       </c>
       <c r="H9" t="n">
         <v>1</v>
@@ -819,12 +819,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0700.HK</t>
+          <t>0836.HK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0700.HK</t>
+          <t>0836.HK</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -833,13 +833,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2.92</v>
+        <v>0.8</v>
       </c>
       <c r="E10" t="n">
-        <v>19.91</v>
+        <v>9.77</v>
       </c>
       <c r="F10" t="n">
-        <v>1.23</v>
+        <v>5.77</v>
       </c>
       <c r="G10" t="n">
         <v>0.38</v>
@@ -861,30 +861,30 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0836.HK</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0836.HK</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>港股</t>
+          <t>美股</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.8100000000000001</v>
+        <v>2.54</v>
       </c>
       <c r="E11" t="n">
-        <v>9.77</v>
+        <v>17.79</v>
       </c>
       <c r="F11" t="n">
-        <v>5.77</v>
+        <v>1.87</v>
       </c>
       <c r="G11" t="n">
-        <v>0.381</v>
+        <v>0.399</v>
       </c>
       <c r="H11" t="n">
         <v>1</v>
@@ -903,30 +903,30 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>0700.HK</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>0700.HK</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>美股</t>
+          <t>港股</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2.65</v>
+        <v>3.07</v>
       </c>
       <c r="E12" t="n">
-        <v>17.79</v>
+        <v>19.91</v>
       </c>
       <c r="F12" t="n">
-        <v>1.89</v>
+        <v>1.23</v>
       </c>
       <c r="G12" t="n">
-        <v>0.415</v>
+        <v>0.399</v>
       </c>
       <c r="H12" t="n">
         <v>1</v>
@@ -968,7 +968,7 @@
         <v>5.85</v>
       </c>
       <c r="G13" t="n">
-        <v>0.44</v>
+        <v>0.442</v>
       </c>
       <c r="H13" t="n">
         <v>1</v>
@@ -1001,16 +1001,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>19.61</v>
+        <v>19.1</v>
       </c>
       <c r="E14" t="n">
         <v>61.19</v>
       </c>
       <c r="F14" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G14" t="n">
-        <v>0.474</v>
+        <v>0.461</v>
       </c>
       <c r="H14" t="n">
         <v>1</v>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>8.15</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="E15" t="n">
         <v>33.57</v>
@@ -1052,7 +1052,7 @@
         <v>3.8</v>
       </c>
       <c r="G15" t="n">
-        <v>0.588</v>
+        <v>0.597</v>
       </c>
       <c r="H15" t="n">
         <v>1</v>
@@ -1085,7 +1085,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2.26</v>
+        <v>2.23</v>
       </c>
       <c r="E16" t="n">
         <v>12.63</v>
@@ -1094,7 +1094,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.767</v>
+        <v>0.756</v>
       </c>
       <c r="H16" t="n">
         <v>0.75</v>
@@ -1136,7 +1136,7 @@
         <v>6.84</v>
       </c>
       <c r="G17" t="n">
-        <v>0.82</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="H17" t="n">
         <v>1</v>
